--- a/output/月度核算报表_Phase1.xlsx
+++ b/output/月度核算报表_Phase1.xlsx
@@ -215,8 +215,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -232,7 +240,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -240,13 +248,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,34 +575,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -907,7 +933,7 @@
         <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13">
         <v>4417</v>
@@ -965,7 +991,7 @@
         <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15">
         <v>4419</v>
